--- a/mode_docx_gen/pmi_ka/uv_modes/УВ_6.xlsx
+++ b/mode_docx_gen/pmi_ka/uv_modes/УВ_6.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>SGF13_tsa</t>
+          <t>SGF13_lvalh</t>
         </is>
       </c>
     </row>
@@ -683,8 +683,8 @@
       <c r="Z2" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="AA2" s="2" t="n">
-        <v>1</v>
+      <c r="AA2" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -853,7 +853,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM2"/>
+  <dimension ref="A1:AL2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -894,7 +894,6 @@
     <col width="20" customWidth="1" min="36" max="36"/>
     <col width="20" customWidth="1" min="37" max="37"/>
     <col width="20" customWidth="1" min="38" max="38"/>
-    <col width="20" customWidth="1" min="39" max="39"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1075,20 +1074,15 @@
       </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
-          <t>oper_otkl_v</t>
+          <t>pusk_urov_vnesh</t>
         </is>
       </c>
       <c r="AK1" s="1" t="inlineStr">
         <is>
-          <t>pusk_urov_vnesh</t>
+          <t>vnesh_otkl_zdz</t>
         </is>
       </c>
       <c r="AL1" s="1" t="inlineStr">
-        <is>
-          <t>vnesh_otkl_zdz</t>
-        </is>
-      </c>
-      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>vnesh_otkl_urov</t>
         </is>
@@ -1207,9 +1201,6 @@
         <v>0</v>
       </c>
       <c r="AL2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM2" t="n">
         <v>0</v>
       </c>
     </row>
